--- a/education_forms/049_scientific_principles_quiz--education_forms.xlsx
+++ b/education_forms/049_scientific_principles_quiz--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,20 +525,20 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ScientificPrinciplesQuiz</t>
+          <t>What is the fundamental principle behind the scientific method?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -548,13 +548,13 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>scientific_principles</t>
+          <t>Why is it essential to conduct a thorough literature review in scientific research?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -571,13 +571,13 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ScientificPrinciplesQuiz</t>
+          <t>What is the scientific method for testing hypotheses?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -594,20 +594,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>scientificprinciples</t>
+          <t>What is the difference between a controlled experiment and an observational study?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -617,20 +617,20 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ScientificPrinciples</t>
+          <t>How do scientists use probability and statistics in their research?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>scientific_principles</t>
+          <t>What is the importance of peer review in scientific research?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -663,20 +663,20 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>scientific_principles_quiz</t>
+          <t>What is the role of sampling techniques in scientific research?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>scientific_principles_quiz</t>
+          <t>How do scientists use descriptive and analytical research methods?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,7 +699,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -709,13 +709,13 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>scientific_principles_quiz</t>
+          <t>What is the difference between a dependent and independent variable?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -732,13 +732,13 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>scientific_principles_quiz</t>
+          <t>How do scientists use statistical analysis in their research?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -755,13 +755,13 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>scientific_principles_quiz</t>
+          <t>What is the importance of ethics in scientific research?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -778,20 +778,20 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>scientific_principles</t>
+          <t>What are the key principles of scientific communication?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -801,13 +801,13 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>scientific_principles</t>
+          <t>What is the role of technology in scientific research?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -824,13 +824,13 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>scientific_principles</t>
+          <t>How do scientists use data collection and data analysis?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -847,20 +847,20 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>scientific_principles</t>
+          <t>What is the importance of reproducibility in scientific research?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>scientific_principles_quiz</t>
+          <t>What is the role of peer review in scientific research?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -883,7 +883,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -893,13 +893,13 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>scientific_principles_quiz</t>
+          <t>What is the role of ethics in scientific research?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -916,20 +916,20 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>scientific_principles</t>
+          <t>What is the importance of data visualization?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>scientific_principles</t>
+          <t>Scientific Principles Quiz Form 19</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -952,7 +952,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>scientific_principles_quiz</t>
+          <t>What is the importance of research funding?</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -975,7 +975,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -985,13 +985,13 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>scientific_principles_quiz</t>
+          <t>What is the role of collaboration in scientific research?</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1008,20 +1008,20 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>scientific_principles</t>
+          <t>What is the importance of literature review in scientific research?</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1031,13 +1031,13 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>scientific_principles_quiz</t>
+          <t>What is the role of hypothesis testing?</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1054,20 +1054,20 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>scientific_principles</t>
+          <t>What is the importance of data analysis in scientific research?</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1077,13 +1077,13 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>scientific_principles_quiz</t>
+          <t>What is the role of replication?</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1098,12 +1098,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
-    <col width="47" customWidth="1" min="2" max="2"/>
-    <col width="47" customWidth="1" min="3" max="3"/>
+    <col width="49" customWidth="1" min="2" max="2"/>
+    <col width="49" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_3.1,_'label':_'scientificprinciples'}</t>
+          <t>null_hypothesis</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 3.1, 'label': 'ScientificPrinciples'}</t>
+          <t>Null Hypothesis</t>
         </is>
       </c>
     </row>
@@ -1148,182 +1148,114 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_3.2,_'label':_'scientificprinciples2'}</t>
+          <t>alternative_hypothesis</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 3.2, 'label': 'ScientificPrinciples2'}</t>
+          <t>Alternative Hypothesis</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>scientific_principles_quiz_form_3_choices</t>
+          <t>scientific_principles_quiz_form_6_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3.3,_'label':_'scientificprinciples3'}</t>
+          <t>ensures_quality_control</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3.3, 'label': 'ScientificPrinciples3'}</t>
+          <t>Ensures quality control</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>scientific_principles_quiz_form_3_choices</t>
+          <t>scientific_principles_quiz_form_6_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_3.4,_'label':_'scientificprinciples4'}</t>
+          <t>promotes_collaboration_and_feedback</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 3.4, 'label': 'ScientificPrinciples4'}</t>
+          <t>Promotes collaboration and feedback</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>scientific_principles_quiz_form_8_choices</t>
+          <t>scientific_principles_quiz_form_6_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_8.1,_'label':_'scientificprinciples'}</t>
+          <t>provides_credibility_and_accountability</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 8.1, 'label': 'ScientificPrinciples'}</t>
+          <t>Provides credibility and accountability</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>scientific_principles_quiz_form_8_choices</t>
+          <t>scientific_principles_quiz_form_16_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_8.2,_'label':_'scientificprinciples2'}</t>
+          <t>ensures_quality_control</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 8.2, 'label': 'ScientificPrinciples2'}</t>
+          <t>Ensures quality control</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>scientific_principles_quiz_form_8_choices</t>
+          <t>scientific_principles_quiz_form_16_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_8.3,_'label':_'scientificprinciples3'}</t>
+          <t>provides_feedback_and_improvement_opportunities</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 8.3, 'label': 'ScientificPrinciples3'}</t>
+          <t>Provides feedback and improvement opportunities</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>scientific_principles_quiz_form_19_choices</t>
+          <t>scientific_principles_quiz_form_16_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_19.1,_'label':_'option1'}</t>
+          <t>promotes_credibility_and_accountability</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 19.1, 'label': 'Option1'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>scientific_principles_quiz_form_19_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>{'id':_19.2,_'label':_'option2'}</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>{'id': 19.2, 'label': 'Option2'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>scientific_principles_quiz_form_19_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>{'id':_19.3,_'label':_'option3'}</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>{'id': 19.3, 'label': 'Option3'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>scientific_principles_quiz_form_20_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>{'id':_20.1,_'label':_'option1'}</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>{'id': 20.1, 'label': 'Option1'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>scientific_principles_quiz_form_20_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>{'id':_20.2,_'label':_'option2'}</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>{'id': 20.2, 'label': 'Option2'}</t>
+          <t>Promotes credibility and accountability</t>
         </is>
       </c>
     </row>
